--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
@@ -47,7 +47,7 @@
     <t>{dept}</t>
   </si>
   <si>
-    <t>{year}年{month}月{day}日</t>
+    <t>{yearMonthDay}</t>
   </si>
   <si>
     <t>财务收单编码：</t>
@@ -83,13 +83,13 @@
     <t>人民币(小写）：</t>
   </si>
   <si>
-    <t>{lowAmount}</t>
+    <t>￥{lowAmountQian}</t>
   </si>
   <si>
     <t>预计归还时间</t>
   </si>
   <si>
-    <t>{returnDate}</t>
+    <t>{returnDateStr}</t>
   </si>
   <si>
     <t>总经理：</t>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
@@ -838,7 +838,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -852,10 +852,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -883,6 +883,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -897,6 +906,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1296,14 +1308,14 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="24.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.25" customWidth="1"/>
-    <col min="8" max="8" width="15.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.125" customWidth="1"/>
+    <col min="8" max="8" width="19.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="75" customHeight="1" spans="1:8">
@@ -1364,27 +1376,27 @@
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="13"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="16"/>
     </row>
     <row r="5" ht="65.1" customHeight="1" spans="1:8">
       <c r="A5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="14"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="10" t="s">
@@ -1396,9 +1408,9 @@
       <c r="A6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="19"/>
       <c r="E6" s="10" t="s">
         <v>19</v>
       </c>
@@ -1407,99 +1419,99 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="65.1" customHeight="1" spans="1:8">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18" t="s">
+      <c r="B7" s="20"/>
+      <c r="C7" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18" t="s">
+      <c r="D7" s="21"/>
+      <c r="E7" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="22" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
     </row>
     <row r="9" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21"/>
     </row>
     <row r="10" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21"/>
     </row>
     <row r="11" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="12" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21"/>
     </row>
     <row r="13" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
     </row>
     <row r="14" ht="72" customHeight="1"/>
     <row r="15" ht="60" customHeight="1" spans="1:8">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
     </row>
     <row r="16" ht="60" customHeight="1" spans="1:8">
       <c r="A16" s="3" t="s">
@@ -1547,21 +1559,21 @@
       <c r="A18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="13"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="16"/>
     </row>
     <row r="19" ht="60" customHeight="1" spans="1:8">
       <c r="A19" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="14"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="10" t="s">
         <v>15</v>
       </c>
@@ -1579,9 +1591,9 @@
       <c r="A20" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="16"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="19"/>
       <c r="E20" s="10" t="s">
         <v>19</v>
       </c>
@@ -1590,24 +1602,24 @@
       <c r="H20" s="13"/>
     </row>
     <row r="21" ht="60" customHeight="1" spans="1:8">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="18" t="s">
+      <c r="D21" s="20"/>
+      <c r="E21" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="17" t="s">
+      <c r="G21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="H21" s="18" t="s">
+      <c r="H21" s="22" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1639,7 +1651,7 @@
     <mergeCell ref="E20:H20"/>
   </mergeCells>
   <pageMargins left="0.998611111111111" right="0.998611111111111" top="0.998611111111111" bottom="0.998611111111111" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="53" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="26">
   <si>
     <t>借支单</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>{debitSign}</t>
+  </si>
+  <si>
+    <t>裁切线</t>
   </si>
 </sst>
 </file>
@@ -118,7 +121,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -161,13 +164,20 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <u val="double"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -512,7 +522,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -587,6 +597,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dashed">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -693,152 +712,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -852,10 +871,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -883,15 +902,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -908,13 +918,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1308,14 +1324,14 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="24.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.125" customWidth="1"/>
-    <col min="8" max="8" width="19.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.25" customWidth="1"/>
+    <col min="8" max="8" width="15.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="75" customHeight="1" spans="1:8">
@@ -1376,27 +1392,27 @@
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="13"/>
     </row>
     <row r="5" ht="65.1" customHeight="1" spans="1:8">
       <c r="A5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="17"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18" t="s">
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="10" t="s">
@@ -1408,9 +1424,9 @@
       <c r="A6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="19"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="10" t="s">
         <v>19</v>
       </c>
@@ -1419,99 +1435,101 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="65.1" customHeight="1" spans="1:8">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21" t="s">
+      <c r="D7" s="18"/>
+      <c r="E7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="18" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="21"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="21"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" ht="42.95" customHeight="1" spans="1:8">
       <c r="A11" s="20"/>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="21"/>
+      <c r="D11" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="22"/>
       <c r="F11" s="23"/>
       <c r="G11" s="20"/>
-      <c r="H11" s="21"/>
+      <c r="H11" s="22"/>
     </row>
     <row r="12" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="21"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A13" s="20"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="21"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" ht="72" customHeight="1"/>
-    <row r="15" ht="60" customHeight="1" spans="1:8">
-      <c r="A15" s="24" t="s">
+    <row r="15" ht="75" customHeight="1" spans="1:8">
+      <c r="A15" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
     </row>
     <row r="16" ht="60" customHeight="1" spans="1:8">
       <c r="A16" s="3" t="s">
@@ -1559,21 +1577,21 @@
       <c r="A18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="13"/>
     </row>
     <row r="19" ht="60" customHeight="1" spans="1:8">
       <c r="A19" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="17"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="10" t="s">
         <v>15</v>
       </c>
@@ -1591,9 +1609,9 @@
       <c r="A20" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="19"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="16"/>
       <c r="E20" s="10" t="s">
         <v>19</v>
       </c>
@@ -1602,24 +1620,24 @@
       <c r="H20" s="13"/>
     </row>
     <row r="21" ht="60" customHeight="1" spans="1:8">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20" t="s">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="21" t="s">
+      <c r="D21" s="17"/>
+      <c r="E21" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="F21" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="20" t="s">
+      <c r="G21" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="H21" s="22" t="s">
+      <c r="H21" s="18" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1651,7 +1669,7 @@
     <mergeCell ref="E20:H20"/>
   </mergeCells>
   <pageMargins left="0.998611111111111" right="0.998611111111111" top="0.998611111111111" bottom="0.998611111111111" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="51" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="53" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23775" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="3.借支单" sheetId="3" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>借支单</t>
   </si>
@@ -105,9 +105,6 @@
   </si>
   <si>
     <t>{debitSign}</t>
-  </si>
-  <si>
-    <t>裁切线</t>
   </si>
 </sst>
 </file>
@@ -121,7 +118,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -172,12 +169,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -522,7 +513,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -597,15 +588,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="dashed">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -712,148 +694,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -920,16 +902,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1490,9 +1472,7 @@
       <c r="A11" s="20"/>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="s">
-        <v>25</v>
-      </c>
+      <c r="D11" s="21"/>
       <c r="E11" s="22"/>
       <c r="F11" s="23"/>
       <c r="G11" s="20"/>
@@ -1677,7 +1657,7 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
-  <rangeList sheetStid="3" master="">
+  <rangeList sheetStid="3" master="" otherUserPermission="visible">
     <arrUserId title="区域1" rangeCreator="" othersAccessPermission="edit"/>
   </rangeList>
 </allowEditUser>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
@@ -10,7 +10,7 @@
     <sheet name="3.借支单" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'3.借支单'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'3.借支单'!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -118,7 +118,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -134,27 +134,20 @@
     </font>
     <font>
       <b/>
-      <sz val="22"/>
+      <sz val="36"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -694,152 +687,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -850,48 +843,57 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -902,16 +904,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -980,11 +994,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>635</xdr:colOff>
+      <xdr:colOff>9525</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>635</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1994535" cy="588010"/>
+    <xdr:ext cx="2190115" cy="941070"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="图片 1"/>
@@ -998,8 +1012,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="635" y="635"/>
-          <a:ext cx="1994535" cy="588010"/>
+          <a:off x="9525" y="9525"/>
+          <a:ext cx="2190115" cy="941070"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1011,11 +1025,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>635</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>20955</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1994535" cy="588010"/>
+    <xdr:ext cx="2130425" cy="968375"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="图片 1"/>
@@ -1029,8 +1043,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="635" y="9751695"/>
-          <a:ext cx="1994535" cy="588010"/>
+          <a:off x="9525" y="12893040"/>
+          <a:ext cx="2130425" cy="968375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1303,17 +1317,17 @@
     <tabColor rgb="FFFFFF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.25" customWidth="1"/>
-    <col min="8" max="8" width="15.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.2583333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.4916666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.9916666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.9666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27.8" style="1" customWidth="1"/>
+    <col min="7" max="7" width="26.6166666666667" customWidth="1"/>
+    <col min="8" max="8" width="46.6833333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="75" customHeight="1" spans="1:8">
@@ -1328,7 +1342,7 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:8">
+    <row r="2" ht="80" customHeight="1" spans="1:8">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1352,7 +1366,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="65.1" customHeight="1" spans="1:8">
+    <row r="3" ht="80" customHeight="1" spans="1:8">
       <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
@@ -1370,7 +1384,7 @@
       </c>
       <c r="H3" s="13"/>
     </row>
-    <row r="4" ht="65.1" customHeight="1" spans="1:8">
+    <row r="4" ht="80" customHeight="1" spans="1:8">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
@@ -1384,7 +1398,7 @@
       <c r="G4" s="11"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" ht="65.1" customHeight="1" spans="1:8">
+    <row r="5" ht="80" customHeight="1" spans="1:8">
       <c r="A5" s="12" t="s">
         <v>14</v>
       </c>
@@ -1402,7 +1416,7 @@
       </c>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" ht="65.1" customHeight="1" spans="1:8">
+    <row r="6" ht="80" customHeight="1" spans="1:8">
       <c r="A6" s="12" t="s">
         <v>18</v>
       </c>
@@ -1416,7 +1430,7 @@
       <c r="G6" s="11"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" ht="65.1" customHeight="1" spans="1:8">
+    <row r="7" ht="80" customHeight="1" spans="1:8">
       <c r="A7" s="17" t="s">
         <v>20</v>
       </c>
@@ -1431,7 +1445,7 @@
       <c r="F7" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="19" t="s">
         <v>8</v>
       </c>
       <c r="H7" s="18" t="s">
@@ -1439,193 +1453,223 @@
       </c>
     </row>
     <row r="8" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
     </row>
     <row r="9" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21"/>
     </row>
     <row r="10" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21"/>
     </row>
     <row r="11" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="22"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="25"/>
     </row>
     <row r="12" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="29"/>
     </row>
     <row r="13" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
-    </row>
-    <row r="14" ht="72" customHeight="1"/>
-    <row r="15" ht="75" customHeight="1" spans="1:8">
-      <c r="A15" s="2" t="s">
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="29"/>
+    </row>
+    <row r="14" ht="42.95" customHeight="1" spans="1:8">
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="29"/>
+    </row>
+    <row r="15" ht="42.95" customHeight="1" spans="1:8">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="21"/>
+    </row>
+    <row r="16" ht="42.95" customHeight="1" spans="1:8">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="21"/>
+    </row>
+    <row r="17" ht="72" customHeight="1"/>
+    <row r="18" ht="75" customHeight="1" spans="1:8">
+      <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" ht="60" customHeight="1" spans="1:8">
-      <c r="A16" s="3" t="s">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" ht="80" customHeight="1" spans="1:8">
+      <c r="A19" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E19" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="7" t="s">
+      <c r="F19" s="6"/>
+      <c r="G19" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H19" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1" spans="1:8">
-      <c r="A17" s="9" t="s">
+    <row r="20" ht="80" customHeight="1" spans="1:8">
+      <c r="A20" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B20" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="12" t="s">
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G20" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="13"/>
-    </row>
-    <row r="18" ht="60" customHeight="1" spans="1:8">
-      <c r="A18" s="9" t="s">
+      <c r="H20" s="13"/>
+    </row>
+    <row r="21" ht="80" customHeight="1" spans="1:8">
+      <c r="A21" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="13"/>
-    </row>
-    <row r="19" ht="60" customHeight="1" spans="1:8">
-      <c r="A19" s="12" t="s">
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="13"/>
+    </row>
+    <row r="22" ht="80" customHeight="1" spans="1:8">
+      <c r="A22" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="10" t="s">
+      <c r="B22" s="14"/>
+      <c r="C22" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="12" t="s">
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G22" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="13"/>
-    </row>
-    <row r="20" ht="60" customHeight="1" spans="1:8">
-      <c r="A20" s="12" t="s">
+      <c r="H22" s="13"/>
+    </row>
+    <row r="23" ht="80" customHeight="1" spans="1:8">
+      <c r="A23" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="10" t="s">
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="13"/>
-    </row>
-    <row r="21" ht="60" customHeight="1" spans="1:8">
-      <c r="A21" s="17" t="s">
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="13"/>
+    </row>
+    <row r="24" ht="80" customHeight="1" spans="1:8">
+      <c r="A24" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17" t="s">
+      <c r="B24" s="17"/>
+      <c r="C24" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="18" t="s">
+      <c r="D24" s="18"/>
+      <c r="E24" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F24" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="17" t="s">
+      <c r="G24" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H21" s="18" t="s">
+      <c r="H24" s="18" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange password="C6E5" sqref="A21:D21 E21:F21 A17:E17 G17:H17 F17 A18:H18 A19:E19 G19:H19 A20:H20 F19 A1:H15 A16:G16 H16 G21 H21" name="区域1"/>
+    <protectedRange password="C6E5" sqref="A24:D24 E24:F24 A20:E20 G20:H20 F20 A21:H21 A22:E22 G22:H22 A23:H23 F22 A1:H18 A19:G19 H19 G24 H24" name="区域1"/>
   </protectedRanges>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="B3:E3"/>
@@ -1637,19 +1681,20 @@
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="C24:D24"/>
   </mergeCells>
-  <pageMargins left="0.998611111111111" right="0.998611111111111" top="0.998611111111111" bottom="0.998611111111111" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="53" orientation="portrait"/>
+  <pageMargins left="0.550694444444444" right="0.156944444444444" top="0.998611111111111" bottom="0.998611111111111" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="42" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
@@ -1043,7 +1043,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9525" y="12893040"/>
+          <a:off x="9525" y="13591540"/>
           <a:ext cx="2130425" cy="968375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1323,9 +1323,9 @@
     <col min="1" max="1" width="19.2583333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.5833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.4916666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.9916666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7916666666667" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.9666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="27.8" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27.9416666666667" style="1" customWidth="1"/>
     <col min="7" max="7" width="26.6166666666667" customWidth="1"/>
     <col min="8" max="8" width="46.6833333333333" style="1" customWidth="1"/>
   </cols>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H3" s="13"/>
     </row>
-    <row r="4" ht="80" customHeight="1" spans="1:8">
+    <row r="4" ht="135" customHeight="1" spans="1:8">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="H20" s="13"/>
     </row>
-    <row r="21" ht="80" customHeight="1" spans="1:8">
+    <row r="21" ht="135" customHeight="1" spans="1:8">
       <c r="A21" s="9" t="s">
         <v>12</v>
       </c>
@@ -1694,7 +1694,7 @@
     <mergeCell ref="C24:D24"/>
   </mergeCells>
   <pageMargins left="0.550694444444444" right="0.156944444444444" top="0.998611111111111" bottom="0.998611111111111" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="42" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="39" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
@@ -506,7 +506,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -552,6 +552,15 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -561,7 +570,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -708,7 +719,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -720,34 +731,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -832,7 +843,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -845,11 +856,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -868,22 +882,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -927,6 +947,19 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1043,7 +1076,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9525" y="13591540"/>
+          <a:off x="9525" y="15267940"/>
           <a:ext cx="2130425" cy="968375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1321,10 +1354,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="19.2583333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.5833333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.2666666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.4916666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7916666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.9666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.2583333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="35.7333333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="27.9416666666667" style="1" customWidth="1"/>
     <col min="7" max="7" width="26.6166666666667" customWidth="1"/>
     <col min="8" max="8" width="46.6833333333333" style="1" customWidth="1"/>
@@ -1349,200 +1382,200 @@
       <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1" spans="1:8">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="12" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="13"/>
-    </row>
-    <row r="4" ht="135" customHeight="1" spans="1:8">
-      <c r="A4" s="9" t="s">
+      <c r="H3" s="16"/>
+    </row>
+    <row r="4" ht="165" customHeight="1" spans="1:8">
+      <c r="A4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="16"/>
     </row>
     <row r="5" ht="80" customHeight="1" spans="1:8">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="13"/>
+      <c r="H5" s="16"/>
     </row>
     <row r="6" ht="80" customHeight="1" spans="1:8">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="10" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="16"/>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:8">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18" t="s">
+      <c r="B7" s="20"/>
+      <c r="C7" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18" t="s">
+      <c r="D7" s="21"/>
+      <c r="E7" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="21" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="21"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="21"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="25"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="28"/>
     </row>
     <row r="12" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="29"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="32"/>
     </row>
     <row r="13" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="29"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="32"/>
     </row>
     <row r="14" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="29"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="32"/>
     </row>
     <row r="15" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A15" s="20"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="21"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="24"/>
     </row>
     <row r="16" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="21"/>
-    </row>
-    <row r="17" ht="72" customHeight="1"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="24"/>
+    </row>
+    <row r="17" ht="174" customHeight="1"/>
     <row r="18" ht="75" customHeight="1" spans="1:8">
       <c r="A18" s="2" t="s">
         <v>0</v>
@@ -1559,109 +1592,109 @@
       <c r="A19" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="34"/>
+      <c r="D19" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="F19" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="37" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" ht="80" customHeight="1" spans="1:8">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="12" t="s">
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="13"/>
-    </row>
-    <row r="21" ht="135" customHeight="1" spans="1:8">
-      <c r="A21" s="9" t="s">
+      <c r="H20" s="16"/>
+    </row>
+    <row r="21" ht="165" customHeight="1" spans="1:8">
+      <c r="A21" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="16"/>
     </row>
     <row r="22" ht="80" customHeight="1" spans="1:8">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="10" t="s">
+      <c r="B22" s="17"/>
+      <c r="C22" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="15" t="s">
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="13"/>
+      <c r="H22" s="16"/>
     </row>
     <row r="23" ht="80" customHeight="1" spans="1:8">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="10" t="s">
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="16"/>
     </row>
     <row r="24" ht="80" customHeight="1" spans="1:8">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="18" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18" t="s">
+      <c r="D24" s="21"/>
+      <c r="E24" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="H24" s="18" t="s">
+      <c r="H24" s="21" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1671,7 +1704,7 @@
   </protectedRanges>
   <mergeCells count="22">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="B4:H4"/>
@@ -1682,7 +1715,7 @@
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="A18:H18"/>
-    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="B21:H21"/>
@@ -1694,7 +1727,7 @@
     <mergeCell ref="C24:D24"/>
   </mergeCells>
   <pageMargins left="0.550694444444444" right="0.156944444444444" top="0.998611111111111" bottom="0.998611111111111" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="39" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="38" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
@@ -10,7 +10,7 @@
     <sheet name="3.借支单" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'3.借支单'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'3.借支单'!$A$1:$H$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
   <si>
     <t>借支单</t>
   </si>
@@ -92,13 +92,7 @@
     <t>{returnDateStr}</t>
   </si>
   <si>
-    <t>总经理：</t>
-  </si>
-  <si>
-    <t>财务主管：</t>
-  </si>
-  <si>
-    <t>会计：</t>
+    <t>总经理：                   财务主管：                   会计：</t>
   </si>
   <si>
     <t>出纳：</t>
@@ -118,7 +112,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -141,24 +135,37 @@
     </font>
     <font>
       <b/>
+      <sz val="22"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <u val="double"/>
       <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <u val="double"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -698,28 +705,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -728,122 +726,131 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -854,9 +861,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -907,46 +911,43 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1059,7 +1060,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>20955</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2130425" cy="968375"/>
@@ -1076,7 +1077,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9525" y="15267940"/>
+          <a:off x="9525" y="15282545"/>
           <a:ext cx="2130425" cy="968375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1350,17 +1351,17 @@
     <tabColor rgb="FFFFFF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="19.2583333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5833333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="39.2666666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.4916666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.2583333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="35.7333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="27.9416666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="26.6166666666667" customWidth="1"/>
-    <col min="8" max="8" width="46.6833333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="41.1333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.675" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29.9916666666667" customWidth="1"/>
+    <col min="8" max="8" width="39.0833333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="75" customHeight="1" spans="1:8">
@@ -1382,110 +1383,106 @@
       <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1" spans="1:8">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="14" t="s">
+      <c r="C3" s="11"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="16"/>
-    </row>
-    <row r="4" ht="165" customHeight="1" spans="1:8">
-      <c r="A4" s="10" t="s">
+      <c r="H3" s="15"/>
+    </row>
+    <row r="4" ht="230" customHeight="1" spans="1:8">
+      <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="16"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="15"/>
     </row>
     <row r="5" ht="80" customHeight="1" spans="1:8">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18" t="s">
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="16"/>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" ht="80" customHeight="1" spans="1:8">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="15" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="16"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="15"/>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:8">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21" t="s">
+      <c r="G7" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" ht="42.95" customHeight="1" spans="1:8">
+    </row>
+    <row r="8" ht="65" customHeight="1" spans="1:8">
       <c r="A8" s="23"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
@@ -1496,24 +1493,24 @@
       <c r="H8" s="24"/>
     </row>
     <row r="9" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
+      <c r="A9" s="26"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="28"/>
     </row>
     <row r="10" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="24"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="28"/>
     </row>
     <row r="11" ht="42.95" customHeight="1" spans="1:8">
       <c r="A11" s="26"/>
@@ -1526,181 +1523,167 @@
       <c r="H11" s="28"/>
     </row>
     <row r="12" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="32"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="24"/>
     </row>
     <row r="13" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="32"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="24"/>
     </row>
     <row r="14" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="32"/>
-    </row>
-    <row r="15" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A15" s="23"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="24"/>
-    </row>
-    <row r="16" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="24"/>
-    </row>
-    <row r="17" ht="174" customHeight="1"/>
-    <row r="18" ht="75" customHeight="1" spans="1:8">
-      <c r="A18" s="2" t="s">
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
+    </row>
+    <row r="15" ht="174" customHeight="1" spans="1:8">
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="30"/>
+    </row>
+    <row r="16" ht="75" customHeight="1" spans="1:8">
+      <c r="A16" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" ht="80" customHeight="1" spans="1:8">
-      <c r="A19" s="3" t="s">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" ht="80" customHeight="1" spans="1:8">
+      <c r="A17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B17" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="35" t="s">
+      <c r="C17" s="32"/>
+      <c r="D17" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E17" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="37" t="s">
+      <c r="H17" s="35" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="18" ht="80" customHeight="1" spans="1:8">
+      <c r="A18" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="15"/>
+    </row>
+    <row r="19" ht="230" customHeight="1" spans="1:8">
+      <c r="A19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="15"/>
+    </row>
     <row r="20" ht="80" customHeight="1" spans="1:8">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="C20" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="15"/>
+    </row>
+    <row r="21" ht="80" customHeight="1" spans="1:8">
+      <c r="A21" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="15"/>
+    </row>
+    <row r="22" ht="80" customHeight="1" spans="1:8">
+      <c r="A22" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="16"/>
-    </row>
-    <row r="21" ht="165" customHeight="1" spans="1:8">
-      <c r="A21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="16"/>
-    </row>
-    <row r="22" ht="80" customHeight="1" spans="1:8">
-      <c r="A22" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="16"/>
-    </row>
-    <row r="23" ht="80" customHeight="1" spans="1:8">
-      <c r="A23" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="16"/>
-    </row>
-    <row r="24" ht="80" customHeight="1" spans="1:8">
-      <c r="A24" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21" t="s">
+      <c r="H22" s="22" t="s">
         <v>22</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" s="21" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange password="C6E5" sqref="A24:D24 E24:F24 A20:E20 G20:H20 F20 A21:H21 A22:E22 G22:H22 A23:H23 F22 A1:H18 A19:G19 H19 G24 H24" name="区域1"/>
+    <protectedRange password="C6E5" sqref="A18:E18 G18:H18 F18 A19:H19 A20:E20 G20:H20 A21:H21 F20 A17:G17 H17 G22 H22 A1:H6 F7:H7 A8:H16 F22" name="区域1"/>
+    <protectedRange sqref="A7:E7 A22:E22" name="区域1_1"/>
   </protectedRanges>
   <mergeCells count="22">
     <mergeCell ref="A1:H1"/>
@@ -1713,21 +1696,21 @@
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="E6:H6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:E20"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.550694444444444" right="0.156944444444444" top="0.998611111111111" bottom="0.998611111111111" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="38" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="35" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1737,6 +1720,7 @@
 <allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
   <rangeList sheetStid="3" master="" otherUserPermission="visible">
     <arrUserId title="区域1" rangeCreator="" othersAccessPermission="edit"/>
+    <arrUserId title="区域1_1" rangeCreator="" othersAccessPermission="edit"/>
   </rangeList>
 </allowEditUser>
 </file>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="22">
   <si>
     <t>借支单</t>
   </si>
@@ -92,10 +92,7 @@
     <t>{returnDateStr}</t>
   </si>
   <si>
-    <t>总经理：                   财务主管：                   会计：</t>
-  </si>
-  <si>
-    <t>出纳：</t>
+    <t>总经理：        财务主管：       会计：       出纳：       部门负责人：        分管领导：</t>
   </si>
   <si>
     <t>{debitSign}</t>
@@ -850,7 +847,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -911,16 +908,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1472,95 +1463,93 @@
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
       <c r="E7" s="19"/>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="19"/>
+      <c r="G7" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="22" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="8" ht="65" customHeight="1" spans="1:8">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="28"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="28"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="26"/>
     </row>
     <row r="11" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="28"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="26"/>
     </row>
     <row r="12" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="24"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
     </row>
     <row r="13" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="24"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="22"/>
     </row>
     <row r="14" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="24"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
     </row>
     <row r="15" ht="174" customHeight="1" spans="1:8">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="30"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="28"/>
     </row>
     <row r="16" ht="75" customHeight="1" spans="1:8">
       <c r="A16" s="2" t="s">
@@ -1578,14 +1567,14 @@
       <c r="A17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="33" t="s">
+      <c r="C17" s="30"/>
+      <c r="D17" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="32" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="6" t="s">
@@ -1594,7 +1583,7 @@
       <c r="G17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="35" t="s">
+      <c r="H17" s="33" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1670,20 +1659,18 @@
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="19"/>
+      <c r="G22" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="19" t="s">
         <v>21</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="22" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange password="C6E5" sqref="A18:E18 G18:H18 F18 A19:H19 A20:E20 G20:H20 A21:H21 F20 A17:G17 H17 G22 H22 A1:H6 F7:H7 A8:H16 F22" name="区域1"/>
-    <protectedRange sqref="A7:E7 A22:E22" name="区域1_1"/>
+    <protectedRange password="C6E5" sqref="A18:E18 G18:H18 F18 A19:H19 A20:E20 G20:H20 A21:H21 F20 A17:G17 H17 A1:H6 F7:H7 A8:H16" name="区域1"/>
+    <protectedRange sqref="A7:E7" name="区域1_1"/>
   </protectedRanges>
   <mergeCells count="22">
     <mergeCell ref="A1:H1"/>
@@ -1696,7 +1683,7 @@
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="E6:H6"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:E18"/>
@@ -1707,7 +1694,7 @@
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="E21:H21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A22:F22"/>
   </mergeCells>
   <pageMargins left="0.550694444444444" right="0.156944444444444" top="0.998611111111111" bottom="0.998611111111111" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="35" orientation="portrait"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
@@ -92,7 +92,7 @@
     <t>{returnDateStr}</t>
   </si>
   <si>
-    <t>总经理：        财务主管：       会计：       出纳：       部门负责人：        分管领导：</t>
+    <t>总经理：        财务主管：       会计：       出纳：        分管领导：       部门负责人：</t>
   </si>
   <si>
     <t>{debitSign}</t>
@@ -1669,8 +1669,7 @@
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange password="C6E5" sqref="A18:E18 G18:H18 F18 A19:H19 A20:E20 G20:H20 A21:H21 F20 A17:G17 H17 A1:H6 F7:H7 A8:H16" name="区域1"/>
-    <protectedRange sqref="A7:E7" name="区域1_1"/>
+    <protectedRange password="C6E5" sqref="A18:E18 G18:H18 F18 A19:H19 A20:E20 G20:H20 A21:H21 F20 A17:G17 H17 A1:H6 A8:H16 G7:H7" name="区域1"/>
   </protectedRanges>
   <mergeCells count="22">
     <mergeCell ref="A1:H1"/>
@@ -1707,7 +1706,6 @@
 <allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
   <rangeList sheetStid="3" master="" otherUserPermission="visible">
     <arrUserId title="区域1" rangeCreator="" othersAccessPermission="edit"/>
-    <arrUserId title="区域1_1" rangeCreator="" othersAccessPermission="edit"/>
   </rangeList>
 </allowEditUser>
 </file>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
   <si>
     <t>借支单</t>
   </si>
@@ -92,10 +92,12 @@
     <t>{returnDateStr}</t>
   </si>
   <si>
-    <t>总经理：        财务主管：       会计：       出纳：        分管领导：       部门负责人：</t>
-  </si>
-  <si>
-    <t>{debitSign}</t>
+    <t xml:space="preserve">审批：         审核：          复核：        出纳：        分管领导：         部门负责人：           借支人：
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{debitSign}
+</t>
   </si>
 </sst>
 </file>
@@ -847,7 +849,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -909,9 +911,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1349,8 +1348,7 @@
     <col min="2" max="2" width="39.2666666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.4916666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.2583333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="41.1333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.675" style="1" customWidth="1"/>
+    <col min="5" max="6" width="41.1333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="29.9916666666667" customWidth="1"/>
     <col min="8" max="8" width="39.0833333333333" style="1" customWidth="1"/>
   </cols>
@@ -1464,92 +1462,90 @@
       <c r="D7" s="19"/>
       <c r="E7" s="19"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="20" t="s">
-        <v>8</v>
-      </c>
+      <c r="G7" s="19"/>
       <c r="H7" s="19" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" ht="65" customHeight="1" spans="1:8">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="22"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
     </row>
     <row r="9" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="26"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="25"/>
     </row>
     <row r="10" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="26"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="25"/>
     </row>
     <row r="11" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A11" s="24"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="26"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="25"/>
     </row>
     <row r="12" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="22"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21"/>
     </row>
     <row r="13" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="22"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
     </row>
     <row r="14" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="22"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="21"/>
     </row>
     <row r="15" ht="174" customHeight="1" spans="1:8">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="28"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="27"/>
     </row>
     <row r="16" ht="75" customHeight="1" spans="1:8">
       <c r="A16" s="2" t="s">
@@ -1567,14 +1563,14 @@
       <c r="A17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="31" t="s">
+      <c r="C17" s="29"/>
+      <c r="D17" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="31" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="6" t="s">
@@ -1583,7 +1579,7 @@
       <c r="G17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="33" t="s">
+      <c r="H17" s="32" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1660,16 +1656,14 @@
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
       <c r="F22" s="19"/>
-      <c r="G22" s="20" t="s">
-        <v>8</v>
-      </c>
+      <c r="G22" s="19"/>
       <c r="H22" s="19" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange password="C6E5" sqref="A18:E18 G18:H18 F18 A19:H19 A20:E20 G20:H20 A21:H21 F20 A17:G17 H17 A1:H6 A8:H16 G7:H7" name="区域1"/>
+    <protectedRange password="C6E5" sqref="A18:E18 G18:H18 F18 A19:H19 A20:E20 G20:H20 A21:H21 F20 A17:G17 H17 A1:H6 A8:H16" name="区域1"/>
   </protectedRanges>
   <mergeCells count="22">
     <mergeCell ref="A1:H1"/>
@@ -1682,7 +1676,7 @@
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="E6:H6"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A7:G7"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:E18"/>
@@ -1693,7 +1687,7 @@
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="E21:H21"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <pageMargins left="0.550694444444444" right="0.156944444444444" top="0.998611111111111" bottom="0.998611111111111" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="35" orientation="portrait"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/DebitTemplate.xlsx
@@ -10,7 +10,7 @@
     <sheet name="3.借支单" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'3.借支单'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'3.借支单'!$A$1:$H$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,8 +29,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="C5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+存在多个打款方向</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>借支单</t>
   </si>
@@ -74,6 +106,33 @@
     <t>{reason}</t>
   </si>
   <si>
+    <t>收款账户信息</t>
+  </si>
+  <si>
+    <t>账户名：</t>
+  </si>
+  <si>
+    <t>{bankName}</t>
+  </si>
+  <si>
+    <t>账户号：</t>
+  </si>
+  <si>
+    <t>{bankNo}</t>
+  </si>
+  <si>
+    <t>开户行：</t>
+  </si>
+  <si>
+    <t>{bankAccount}</t>
+  </si>
+  <si>
+    <t>备注：</t>
+  </si>
+  <si>
+    <t>{bankMemo}</t>
+  </si>
+  <si>
     <t>人民币(大写）：</t>
   </si>
   <si>
@@ -92,11 +151,7 @@
     <t>{returnDateStr}</t>
   </si>
   <si>
-    <t xml:space="preserve">审批：         审核：          复核：        出纳：        分管领导：         部门负责人：           借支人：
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{debitSign}
+    <t xml:space="preserve">审批：         审核：         复核：          出纳：        分管领导：            部门负责人：           借支人：{debitSign}
 </t>
   </si>
 </sst>
@@ -111,7 +166,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -146,27 +201,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="20"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <u val="double"/>
-      <sz val="20"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -317,6 +351,17 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -512,7 +557,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -558,7 +603,9 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -576,10 +623,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -589,13 +636,67 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -704,19 +805,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -725,131 +838,119 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -862,10 +963,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -876,7 +980,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -885,72 +989,44 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1020,7 +1096,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2190115" cy="941070"/>
     <xdr:pic>
@@ -1036,39 +1112,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9525" y="9525"/>
+          <a:off x="9525" y="0"/>
           <a:ext cx="2190115" cy="941070"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>20955</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2130425" cy="968375"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 1"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9525" y="15282545"/>
-          <a:ext cx="2130425" cy="968375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1340,8 +1385,9 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FFFFFF00"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="21.5833333333333" style="1" customWidth="1"/>
@@ -1373,45 +1419,45 @@
         <v>2</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1" spans="1:8">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="11"/>
+      <c r="C3" s="12"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
       <c r="F3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="15"/>
+      <c r="H3" s="14"/>
     </row>
-    <row r="4" ht="230" customHeight="1" spans="1:8">
-      <c r="A4" s="9" t="s">
+    <row r="4" ht="140" customHeight="1" spans="1:8">
+      <c r="A4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="12"/>
@@ -1419,280 +1465,137 @@
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
-      <c r="H4" s="15"/>
+      <c r="H4" s="14"/>
     </row>
     <row r="5" ht="80" customHeight="1" spans="1:8">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="14" t="s">
+      <c r="B5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17" t="s">
+      <c r="C5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="15"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" ht="80" customHeight="1" spans="1:8">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="15"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:8">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
       <c r="D7" s="19"/>
       <c r="E7" s="19"/>
       <c r="F7" s="19"/>
       <c r="G7" s="19"/>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="19"/>
+    </row>
+    <row r="8" ht="80" customHeight="1" spans="1:8">
+      <c r="A8" s="20"/>
+      <c r="B8" s="16" t="s">
         <v>21</v>
       </c>
+      <c r="C8" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
     </row>
-    <row r="8" ht="65" customHeight="1" spans="1:8">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="21"/>
+    <row r="9" ht="80" customHeight="1" spans="1:8">
+      <c r="A9" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="14"/>
     </row>
-    <row r="9" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="25"/>
+    <row r="10" ht="80" customHeight="1" spans="1:8">
+      <c r="A10" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="14"/>
     </row>
-    <row r="10" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="25"/>
-    </row>
-    <row r="11" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
+    <row r="11" ht="80" customHeight="1" spans="1:8">
+      <c r="A11" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="24"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="25"/>
-    </row>
-    <row r="12" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="21"/>
-    </row>
-    <row r="13" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A13" s="20"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="21"/>
-    </row>
-    <row r="14" ht="42.95" customHeight="1" spans="1:8">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="21"/>
-    </row>
-    <row r="15" ht="174" customHeight="1" spans="1:8">
-      <c r="A15" s="27"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="27"/>
-    </row>
-    <row r="16" ht="75" customHeight="1" spans="1:8">
-      <c r="A16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" ht="80" customHeight="1" spans="1:8">
-      <c r="A17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" ht="80" customHeight="1" spans="1:8">
-      <c r="A18" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" s="15"/>
-    </row>
-    <row r="19" ht="230" customHeight="1" spans="1:8">
-      <c r="A19" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="15"/>
-    </row>
-    <row r="20" ht="80" customHeight="1" spans="1:8">
-      <c r="A20" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="15"/>
-    </row>
-    <row r="21" ht="80" customHeight="1" spans="1:8">
-      <c r="A21" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="15"/>
-    </row>
-    <row r="22" ht="80" customHeight="1" spans="1:8">
-      <c r="A22" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19" t="s">
-        <v>21</v>
-      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange password="C6E5" sqref="A18:E18 G18:H18 F18 A19:H19 A20:E20 G20:H20 A21:H21 F20 A17:G17 H17 A1:H6 A8:H16" name="区域1"/>
+    <protectedRange password="C6E5" sqref="A3:E3 G3:H3 F3 A4:H4 A9:E9 G9:H9 A10:H10 F9 A2:G2 H2 A1:H1" name="区域1"/>
   </protectedRanges>
-  <mergeCells count="22">
+  <mergeCells count="16">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="B4:H4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A5:A8"/>
   </mergeCells>
   <pageMargins left="0.550694444444444" right="0.156944444444444" top="0.998611111111111" bottom="0.998611111111111" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="35" orientation="portrait"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
